--- a/xls/square_12_tri3_9.xlsx
+++ b/xls/square_12_tri3_9.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>1.9494194583796212</v>
+        <v>1.9494192152922858</v>
       </c>
       <c r="J9">
-        <v>-1.1857803544876286</v>
+        <v>-1.185780534302142</v>
       </c>
       <c r="K9">
-        <v>-0.34823172748892445</v>
+        <v>-0.3482318192061774</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -517,13 +517,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.8989974810518404</v>
+        <v>-1.8989975627803541</v>
       </c>
       <c r="J10">
-        <v>-1.7692508545041525</v>
+        <v>-1.7692509301217547</v>
       </c>
       <c r="K10">
-        <v>-1.1557032219681094</v>
+        <v>-1.1557032622585934</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -552,13 +552,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-1.8939295017432376</v>
+        <v>-1.8939294791976073</v>
       </c>
       <c r="J11">
-        <v>-1.7628254519838134</v>
+        <v>-1.7628254641197376</v>
       </c>
       <c r="K11">
-        <v>-1.0257306519505478</v>
+        <v>-1.0257309160772192</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -587,13 +587,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.8706411227238375</v>
+        <v>-1.870641182170087</v>
       </c>
       <c r="J12">
-        <v>-1.5997507206005597</v>
+        <v>-1.5997507721895419</v>
       </c>
       <c r="K12">
-        <v>-0.6789596026246855</v>
+        <v>-0.6789596560465916</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-1.5288150012746866</v>
+        <v>-1.5288149849479022</v>
       </c>
       <c r="J13">
-        <v>-1.180868411254494</v>
+        <v>-1.1808684147010557</v>
       </c>
       <c r="K13">
-        <v>2.521101683058159</v>
+        <v>2.5211012227876526</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-0.3851260754088411</v>
+        <v>-0.38512608115372715</v>
       </c>
       <c r="J14">
-        <v>-0.3156795121685549</v>
+        <v>-0.31567951491088936</v>
       </c>
       <c r="K14">
-        <v>3.6255753901240433</v>
+        <v>3.6255753737410026</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-0.0021861102067247365</v>
+        <v>-0.0021861102165804686</v>
       </c>
       <c r="J15">
-        <v>-0.001814557257117068</v>
+        <v>-0.0018145572627263223</v>
       </c>
       <c r="K15">
-        <v>3.0300903300839717</v>
+        <v>3.0300903299407045</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -727,13 +727,573 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>2.6799039961827015e-5</v>
+        <v>2.6799039969059023e-5</v>
       </c>
       <c r="J16">
-        <v>-5.764965972629584e-7</v>
+        <v>-5.764965948521365e-7</v>
       </c>
       <c r="K16">
-        <v>2.2007218453109854</v>
+        <v>2.2007218451487898</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>8.245526297065881e-6</v>
+      </c>
+      <c r="J17">
+        <v>3.0707771450031e-6</v>
+      </c>
+      <c r="K17">
+        <v>1.672718874586924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>-1.2706139944862749e-5</v>
+      </c>
+      <c r="J18">
+        <v>-8.149221419887766e-6</v>
+      </c>
+      <c r="K18">
+        <v>1.7001116305892285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>-2.576168116170409e-8</v>
+      </c>
+      <c r="J19">
+        <v>-3.457190311900741e-7</v>
+      </c>
+      <c r="K19">
+        <v>1.4172992131447124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>-4.18712162564041e-7</v>
+      </c>
+      <c r="J20">
+        <v>-4.578339113272209e-7</v>
+      </c>
+      <c r="K20">
+        <v>1.34893473274022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-6.305201518958223e-7</v>
+      </c>
+      <c r="J21">
+        <v>-4.637862508687238e-7</v>
+      </c>
+      <c r="K21">
+        <v>1.231588781070636</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-2.7253806517068963e-7</v>
+      </c>
+      <c r="J22">
+        <v>-1.9745680859652315e-7</v>
+      </c>
+      <c r="K22">
+        <v>1.0086920741828398</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-1.5672780344932085e-7</v>
+      </c>
+      <c r="J23">
+        <v>-1.2576563087661716e-7</v>
+      </c>
+      <c r="K23">
+        <v>0.942885511987061</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-1.351124663233891e-7</v>
+      </c>
+      <c r="J24">
+        <v>-1.1256133108229511e-7</v>
+      </c>
+      <c r="K24">
+        <v>0.9324397411622602</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-1.4544835025437767e-7</v>
+      </c>
+      <c r="J25">
+        <v>-1.2226489484571735e-7</v>
+      </c>
+      <c r="K25">
+        <v>0.954865291831994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-1.4159724113936018e-7</v>
+      </c>
+      <c r="J26">
+        <v>-1.1909073759012579e-7</v>
+      </c>
+      <c r="K26">
+        <v>0.95832800804333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-1.777907506882055e-7</v>
+      </c>
+      <c r="J27">
+        <v>-1.4368475914882631e-7</v>
+      </c>
+      <c r="K27">
+        <v>0.9836972611756482</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-1.3131891802390468e-7</v>
+      </c>
+      <c r="J28">
+        <v>-1.1059609667838755e-7</v>
+      </c>
+      <c r="K28">
+        <v>0.9388894426406552</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-1.3298600402668e-7</v>
+      </c>
+      <c r="J29">
+        <v>-1.1161341424770276e-7</v>
+      </c>
+      <c r="K29">
+        <v>0.9337270203350957</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-1.2511825393887545e-7</v>
+      </c>
+      <c r="J30">
+        <v>-1.0456163814322028e-7</v>
+      </c>
+      <c r="K30">
+        <v>0.917857448561268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-1.2950639549077579e-7</v>
+      </c>
+      <c r="J31">
+        <v>-1.0723944280431934e-7</v>
+      </c>
+      <c r="K31">
+        <v>0.919551719912289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-1.2823490755502878e-7</v>
+      </c>
+      <c r="J32">
+        <v>-1.0626485383428389e-7</v>
+      </c>
+      <c r="K32">
+        <v>0.9184229386993862</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_9.xlsx
+++ b/xls/square_12_tri3_9.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>169</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>294</v>
+      </c>
+      <c r="I7">
+        <v>24.5624336586914</v>
+      </c>
+      <c r="J7">
+        <v>9.362201874204045</v>
+      </c>
+      <c r="K7">
+        <v>9.676696116087504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>169</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>4.85078516624991</v>
+      </c>
+      <c r="J8">
+        <v>1.19836969386668</v>
+      </c>
+      <c r="K8">
+        <v>1.6966359479781516</v>
+      </c>
+    </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>11</v>
